--- a/cotacoes/2026-09-08/fechamento/VERIFICACAO_PRECOS_EPAN_10-09-2026.xlsx
+++ b/cotacoes/2026-09-08/fechamento/VERIFICACAO_PRECOS_EPAN_10-09-2026.xlsx
@@ -3346,7 +3346,7 @@
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>7895858017422</t>
+          <t>7895858017439</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>7895858017309</t>
+          <t>7895858017415</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
@@ -4740,7 +4740,7 @@
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>000001355406</t>
+          <t>7891137003889</t>
         </is>
       </c>
       <c r="D99" s="5" t="inlineStr">
@@ -9827,7 +9827,7 @@
       </c>
       <c r="C116" s="6" t="inlineStr">
         <is>
-          <t>0000042277217</t>
+          <t>42277217</t>
         </is>
       </c>
       <c r="D116" s="5" t="inlineStr">
@@ -11508,7 +11508,7 @@
       </c>
       <c r="C157" s="6" t="inlineStr">
         <is>
-          <t>7891000319598</t>
+          <t>7891000319581</t>
         </is>
       </c>
       <c r="D157" s="5" t="inlineStr">
@@ -11590,7 +11590,7 @@
       </c>
       <c r="C159" s="6" t="inlineStr">
         <is>
-          <t>7891000062739</t>
+          <t>7891000062722</t>
         </is>
       </c>
       <c r="D159" s="5" t="inlineStr">
@@ -12369,7 +12369,7 @@
       </c>
       <c r="C178" s="6" t="inlineStr">
         <is>
-          <t>47896512900058</t>
+          <t>7896512900050</t>
         </is>
       </c>
       <c r="D178" s="5" t="inlineStr">
@@ -12410,7 +12410,7 @@
       </c>
       <c r="C179" s="6" t="inlineStr">
         <is>
-          <t>37896512912306</t>
+          <t>7896512900166</t>
         </is>
       </c>
       <c r="D179" s="5" t="inlineStr">
